--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/comparison_output/models_comparison_summary.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/comparison_output/models_comparison_summary.xlsx
@@ -515,12 +515,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DHTCUN (baseline)</t>
+          <t>DHTCUN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -569,12 +569,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -623,12 +623,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -677,12 +677,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -731,12 +731,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>OmniSR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -785,12 +785,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -839,12 +839,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>SwinT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -893,12 +893,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -998,7 +998,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DHTCUN (baseline)</t>
+          <t>DHTCUN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DHTCUN (baseline)</t>
+          <t>DHTCUN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1052,7 +1052,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DHTCUN (baseline)</t>
+          <t>DHTCUN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1106,7 +1106,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1214,7 +1214,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1268,7 +1268,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1322,7 +1322,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>OmniSR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>OmniSR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1376,7 +1376,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>OmniSR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1430,7 +1430,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1484,7 +1484,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>SwinT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>SwinT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>SwinT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1565,7 +1565,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1592,7 +1592,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1752,7 +1752,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1808,7 +1808,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1864,7 +1864,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1920,7 +1920,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1976,7 +1976,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2032,7 +2032,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2088,7 +2088,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2144,7 +2144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2200,7 +2200,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2256,7 +2256,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2312,7 +2312,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2368,7 +2368,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2424,7 +2424,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2480,7 +2480,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2536,7 +2536,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2592,7 +2592,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2648,7 +2648,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2704,7 +2704,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2760,7 +2760,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2816,7 +2816,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2872,7 +2872,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2928,7 +2928,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2984,7 +2984,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -3040,7 +3040,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -3096,7 +3096,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -3152,7 +3152,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -3208,7 +3208,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -3264,7 +3264,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3320,7 +3320,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -3376,7 +3376,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -3432,7 +3432,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -3488,7 +3488,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -3544,7 +3544,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -3600,7 +3600,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -3656,7 +3656,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -3712,7 +3712,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -3768,7 +3768,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -3824,7 +3824,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -3880,7 +3880,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -3936,7 +3936,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -3992,7 +3992,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -4048,7 +4048,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -4104,7 +4104,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -4160,7 +4160,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -4216,7 +4216,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -4272,7 +4272,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -4328,7 +4328,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -4384,7 +4384,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -4440,7 +4440,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -4496,7 +4496,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -4552,7 +4552,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -4608,7 +4608,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -4664,7 +4664,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -4720,7 +4720,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -4776,7 +4776,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -4832,7 +4832,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -4888,7 +4888,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -4944,7 +4944,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -5000,7 +5000,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -5056,7 +5056,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -5112,7 +5112,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -5168,7 +5168,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -5224,7 +5224,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -5280,7 +5280,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -5336,7 +5336,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -5392,7 +5392,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -5448,7 +5448,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -5504,7 +5504,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -5560,7 +5560,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -5616,7 +5616,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -5672,7 +5672,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -5728,7 +5728,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -5784,7 +5784,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -5840,7 +5840,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -5896,7 +5896,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -5952,7 +5952,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -6008,7 +6008,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -6064,7 +6064,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -6120,7 +6120,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -6176,7 +6176,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -6232,7 +6232,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -6288,7 +6288,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -6344,7 +6344,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -6400,7 +6400,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -6456,7 +6456,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -6512,7 +6512,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -6568,7 +6568,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -6624,7 +6624,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -6680,7 +6680,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -6736,7 +6736,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -6792,7 +6792,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -6848,7 +6848,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -6904,7 +6904,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -6960,7 +6960,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -7016,7 +7016,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -7072,7 +7072,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -7128,7 +7128,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -7184,7 +7184,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -7240,7 +7240,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -7296,7 +7296,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -7352,7 +7352,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -7408,7 +7408,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -7464,7 +7464,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -7520,7 +7520,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -7576,7 +7576,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -7632,7 +7632,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -7688,7 +7688,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -7744,7 +7744,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -7802,7 +7802,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -7860,7 +7860,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -7918,7 +7918,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -7976,7 +7976,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -8034,7 +8034,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -8092,7 +8092,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -8150,7 +8150,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -8208,7 +8208,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -8266,7 +8266,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -8324,7 +8324,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -8382,7 +8382,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -8440,7 +8440,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -8498,7 +8498,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -8556,7 +8556,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -8614,7 +8614,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -8672,7 +8672,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -8730,7 +8730,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -8788,7 +8788,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -8846,7 +8846,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -8904,7 +8904,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -8962,7 +8962,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -9020,7 +9020,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -9078,7 +9078,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -9136,7 +9136,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -9194,7 +9194,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -9252,7 +9252,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -9310,7 +9310,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -9368,7 +9368,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -9426,7 +9426,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -9484,7 +9484,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -9542,7 +9542,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -9600,7 +9600,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -9658,7 +9658,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -9716,7 +9716,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -9774,7 +9774,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -9832,7 +9832,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -9890,7 +9890,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -9948,7 +9948,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -10006,7 +10006,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -10064,7 +10064,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -10122,7 +10122,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -10180,7 +10180,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -10238,7 +10238,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -10296,7 +10296,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -10354,7 +10354,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -10412,7 +10412,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -10470,7 +10470,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -10528,7 +10528,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -10586,7 +10586,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -10644,7 +10644,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -10702,7 +10702,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -10760,7 +10760,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -10818,7 +10818,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -10876,7 +10876,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -10934,7 +10934,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -10992,7 +10992,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -11050,7 +11050,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -11108,7 +11108,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -11166,7 +11166,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -11224,7 +11224,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -11282,7 +11282,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -11340,7 +11340,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -11398,7 +11398,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -11456,7 +11456,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -11514,7 +11514,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -11572,7 +11572,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -11630,7 +11630,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -11686,7 +11686,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -11742,7 +11742,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -11798,7 +11798,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -11854,7 +11854,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -11910,7 +11910,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -11966,7 +11966,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -12022,7 +12022,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -12078,7 +12078,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -12134,7 +12134,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -12190,7 +12190,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -12246,7 +12246,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -12302,7 +12302,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -12358,7 +12358,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -12414,7 +12414,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -12470,7 +12470,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -12526,7 +12526,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -12582,7 +12582,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -12638,7 +12638,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -12694,7 +12694,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -12750,7 +12750,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -12806,7 +12806,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -12862,7 +12862,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -12918,7 +12918,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -12974,7 +12974,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -13030,7 +13030,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -13086,7 +13086,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -13142,7 +13142,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -13198,7 +13198,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -13254,7 +13254,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -13310,7 +13310,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -13366,7 +13366,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -13422,7 +13422,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -13478,7 +13478,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -13534,7 +13534,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -13590,7 +13590,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -13646,7 +13646,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -13702,7 +13702,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -13758,7 +13758,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -13814,7 +13814,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -13870,7 +13870,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -13926,7 +13926,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -13982,7 +13982,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -14038,7 +14038,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -14094,7 +14094,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -14150,7 +14150,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -14206,7 +14206,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -14262,7 +14262,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -14318,7 +14318,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -14374,7 +14374,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -14430,7 +14430,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -14486,7 +14486,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -14542,7 +14542,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -14598,7 +14598,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B229" t="n">
